--- a/reports/cashier-pdf-reports_cache_report:XII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XII.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>6781</x:v>
+        <x:v>7501</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1831</x:v>
+        <x:v>1951</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>58808</x:v>
+        <x:v>59648</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XII.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>480</x:v>
+        <x:v>960</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4030</x:v>
+        <x:v>7340</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>180</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>961</x:v>
+        <x:v>1681</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>23581</x:v>
+        <x:v>35521</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4030</x:v>
+        <x:v>7340</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2279,7 +2279,7 @@
       <x:c r="N28" s="56" t="s"/>
       <x:c r="O28" s="58" t="s"/>
       <x:c r="P28" s="60" t="n">
-        <x:v>3250</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>12000</x:v>
+        <x:v>12840</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>7501</x:v>
+        <x:v>13921</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>541</x:v>
+        <x:v>1001</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>541</x:v>
+        <x:v>1001</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2419,7 +2419,7 @@
       <x:c r="N34" s="56" t="s"/>
       <x:c r="O34" s="58" t="s"/>
       <x:c r="P34" s="60" t="n">
-        <x:v>300</x:v>
+        <x:v>1260</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>301</x:v>
+        <x:v>401</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1951</x:v>
+        <x:v>3421</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>59648</x:v>
+        <x:v>91578</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XII.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>960</x:v>
+        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>7340</x:v>
+        <x:v>4270</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>300</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>1681</x:v>
+        <x:v>961</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>35521</x:v>
+        <x:v>23581</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>7340</x:v>
+        <x:v>4270</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2279,7 +2279,7 @@
       <x:c r="N28" s="56" t="s"/>
       <x:c r="O28" s="58" t="s"/>
       <x:c r="P28" s="60" t="n">
-        <x:v>5250</x:v>
+        <x:v>3250</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>12840</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>13921</x:v>
+        <x:v>11821</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>1001</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>1001</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2419,7 +2419,7 @@
       <x:c r="N34" s="56" t="s"/>
       <x:c r="O34" s="58" t="s"/>
       <x:c r="P34" s="60" t="n">
-        <x:v>1260</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>401</x:v>
+        <x:v>301</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>3421</x:v>
+        <x:v>2671</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>91578</x:v>
+        <x:v>66128</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:XII.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:XII.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4270</x:v>
+        <x:v>4280</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4270</x:v>
+        <x:v>4280</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>11821</x:v>
+        <x:v>12001</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>1021</x:v>
+        <x:v>1041</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>1021</x:v>
+        <x:v>1041</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>2671</x:v>
+        <x:v>2701</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>66128</x:v>
+        <x:v>66398</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
